--- a/members_data.xlsx
+++ b/members_data.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Waltana\Desktop\EGSA_Lottery_App\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\walfaanaam\Desktop\general\Lottery_app\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="132" yWindow="576" windowWidth="22716" windowHeight="9996"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="10044"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Name</t>
   </si>
@@ -46,12 +46,6 @@
   </si>
   <si>
     <t>977677737</t>
-  </si>
-  <si>
-    <t>926757080</t>
-  </si>
-  <si>
-    <t>Salamoon Zarihun</t>
   </si>
   <si>
     <t>Warqituu Didhaa</t>
@@ -446,7 +440,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.5546875" bestFit="1" customWidth="1"/>
@@ -466,7 +460,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -513,30 +507,30 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
         <v>10</v>
       </c>
-      <c r="B5" t="s">
-        <v>9</v>
-      </c>
       <c r="C5">
         <v>10000</v>
       </c>
       <c r="D5">
-        <v>140000</v>
+        <v>130000</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>11</v>
       </c>
-      <c r="B6" t="s">
-        <v>12</v>
+      <c r="B6">
+        <v>912861288</v>
       </c>
       <c r="C6">
         <v>10000</v>
       </c>
       <c r="D6">
-        <v>130000</v>
+        <v>140000</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -544,40 +538,26 @@
         <v>13</v>
       </c>
       <c r="B7">
-        <v>912861288</v>
+        <v>912356447</v>
       </c>
       <c r="C7">
         <v>10000</v>
       </c>
       <c r="D7">
-        <v>140000</v>
+        <v>80000</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B8">
-        <v>912356447</v>
+        <v>939173232</v>
       </c>
       <c r="C8">
         <v>10000</v>
       </c>
       <c r="D8">
-        <v>80000</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9">
-        <v>939173232</v>
-      </c>
-      <c r="C9">
-        <v>10000</v>
-      </c>
-      <c r="D9">
         <v>130000</v>
       </c>
     </row>

--- a/members_data.xlsx
+++ b/members_data.xlsx
@@ -544,7 +544,7 @@
         <v>10000</v>
       </c>
       <c r="D7">
-        <v>80000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">

--- a/members_data.xlsx
+++ b/members_data.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>Name</t>
   </si>
@@ -46,12 +46,6 @@
   </si>
   <si>
     <t>977677737</t>
-  </si>
-  <si>
-    <t>Warqituu Didhaa</t>
-  </si>
-  <si>
-    <t>935353535</t>
   </si>
   <si>
     <t>Walfaanaa Magarsaa</t>
@@ -440,7 +434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.5546875" bestFit="1" customWidth="1"/>
@@ -460,7 +454,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -509,14 +503,14 @@
       <c r="A5" t="s">
         <v>9</v>
       </c>
-      <c r="B5" t="s">
-        <v>10</v>
+      <c r="B5">
+        <v>912861288</v>
       </c>
       <c r="C5">
         <v>10000</v>
       </c>
       <c r="D5">
-        <v>130000</v>
+        <v>140000</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -524,40 +518,26 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>912861288</v>
+        <v>912356447</v>
       </c>
       <c r="C6">
         <v>10000</v>
       </c>
       <c r="D6">
-        <v>140000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B7">
-        <v>912356447</v>
+        <v>939173232</v>
       </c>
       <c r="C7">
         <v>10000</v>
       </c>
       <c r="D7">
-        <v>50000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8">
-        <v>939173232</v>
-      </c>
-      <c r="C8">
-        <v>10000</v>
-      </c>
-      <c r="D8">
         <v>130000</v>
       </c>
     </row>

--- a/members_data.xlsx
+++ b/members_data.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\walfaanaam\Desktop\general\Lottery_app\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Waltana\Desktop from C\general\Lottery_app\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Name</t>
   </si>
@@ -52,9 +52,6 @@
   </si>
   <si>
     <t>Total money for winners</t>
-  </si>
-  <si>
-    <t>Naggasaa Dheeressaa</t>
   </si>
   <si>
     <t>Oromiyaa Walfaanaa</t>
@@ -434,7 +431,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.5546875" bestFit="1" customWidth="1"/>
@@ -518,26 +515,12 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>912356447</v>
+        <v>939173232</v>
       </c>
       <c r="C6">
         <v>10000</v>
       </c>
       <c r="D6">
-        <v>50000</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7">
-        <v>939173232</v>
-      </c>
-      <c r="C7">
-        <v>10000</v>
-      </c>
-      <c r="D7">
         <v>130000</v>
       </c>
     </row>

--- a/members_data.xlsx
+++ b/members_data.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>Name</t>
   </si>
@@ -34,12 +34,6 @@
   </si>
   <si>
     <t>922956646</t>
-  </si>
-  <si>
-    <t>Lalisee Magarsaa</t>
-  </si>
-  <si>
-    <t>954846351</t>
   </si>
   <si>
     <t>Fayisa Badhu</t>
@@ -431,7 +425,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.5546875" bestFit="1" customWidth="1"/>
@@ -451,7 +445,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -479,21 +473,21 @@
         <v>10000</v>
       </c>
       <c r="D3">
-        <v>140000</v>
+        <v>130000</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>7</v>
       </c>
-      <c r="B4" t="s">
-        <v>8</v>
+      <c r="B4">
+        <v>912861288</v>
       </c>
       <c r="C4">
         <v>10000</v>
       </c>
       <c r="D4">
-        <v>130000</v>
+        <v>140000</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -501,26 +495,12 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>912861288</v>
+        <v>939173232</v>
       </c>
       <c r="C5">
         <v>10000</v>
       </c>
       <c r="D5">
-        <v>140000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6">
-        <v>939173232</v>
-      </c>
-      <c r="C6">
-        <v>10000</v>
-      </c>
-      <c r="D6">
         <v>130000</v>
       </c>
     </row>

--- a/members_data.xlsx
+++ b/members_data.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Name</t>
   </si>
@@ -28,12 +28,6 @@
   </si>
   <si>
     <t>Amount_per_month</t>
-  </si>
-  <si>
-    <t>Lammii Diroo</t>
-  </si>
-  <si>
-    <t>922956646</t>
   </si>
   <si>
     <t>Fayisa Badhu</t>
@@ -425,7 +419,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.5546875" bestFit="1" customWidth="1"/>
@@ -445,7 +439,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -466,14 +460,14 @@
       <c r="A3" t="s">
         <v>5</v>
       </c>
-      <c r="B3" t="s">
-        <v>6</v>
+      <c r="B3">
+        <v>912861288</v>
       </c>
       <c r="C3">
         <v>10000</v>
       </c>
       <c r="D3">
-        <v>130000</v>
+        <v>140000</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -481,26 +475,12 @@
         <v>7</v>
       </c>
       <c r="B4">
-        <v>912861288</v>
+        <v>939173232</v>
       </c>
       <c r="C4">
         <v>10000</v>
       </c>
       <c r="D4">
-        <v>140000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5">
-        <v>939173232</v>
-      </c>
-      <c r="C5">
-        <v>10000</v>
-      </c>
-      <c r="D5">
         <v>130000</v>
       </c>
     </row>

--- a/members_data.xlsx
+++ b/members_data.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>Name</t>
   </si>
@@ -34,9 +34,6 @@
   </si>
   <si>
     <t>977677737</t>
-  </si>
-  <si>
-    <t>Walfaanaa Magarsaa</t>
   </si>
   <si>
     <t>Total money for winners</t>
@@ -419,7 +416,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.5546875" bestFit="1" customWidth="1"/>
@@ -439,7 +436,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -458,29 +455,15 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3">
-        <v>912861288</v>
+        <v>939173232</v>
       </c>
       <c r="C3">
         <v>10000</v>
       </c>
       <c r="D3">
-        <v>140000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4">
-        <v>939173232</v>
-      </c>
-      <c r="C4">
-        <v>10000</v>
-      </c>
-      <c r="D4">
         <v>130000</v>
       </c>
     </row>
